--- a/Employee_Reports_wi52/Vicente Mendigorin Morelos Q0098.xlsx
+++ b/Employee_Reports_wi52/Vicente Mendigorin Morelos Q0098.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5</v>
+        <v>-13</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1019,117 +1019,117 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Truck dock (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-006</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>21-Aug-2024</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Cool Room (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-011</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>29-Sep-2024</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>29-Sep-2026</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Truck dock (Cargo Trainings)</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-M-006</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>EQUIPMENT MANUAL</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>21-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>21-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Cool Room (Cargo Trainings)</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>LSME-CRG-M-011</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>EQUIPMENT MANUAL</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>29-Sep-2024</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>29-Sep-2026</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-317</v>
+        <v>-325</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1399,11 +1399,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-379</v>
+        <v>-387</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
